--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66612A-8732-4319-86E5-CC8E784A5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE93821AEB2AF2A71D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DFC1B3-C613-4495-B80A-EB833725F0DC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 09-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 14-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE93821AEB2AF2A71D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DFC1B3-C613-4495-B80A-EB833725F0DC}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE938042E72B6E270D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D00EC8-AFA7-4454-BD6A-3BD4017F8F97}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE938042E72B6E270D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D00EC8-AFA7-4454-BD6A-3BD4017F8F97}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72E3A41-D3E1-45EC-98E2-8786AA54AFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72E3A41-D3E1-45EC-98E2-8786AA54AFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A87B285-1CD1-4233-9E37-1C09BE5C4ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 14-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 17-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A87B285-1CD1-4233-9E37-1C09BE5C4ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599E562-C9EF-4850-8FA2-43A8D26A3932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599E562-C9EF-4850-8FA2-43A8D26A3932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE9382536759D7C71D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D45B7F2-98EE-4F28-9171-331E3EFC929C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 17-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 18-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE9382536759D7C71D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D45B7F2-98EE-4F28-9171-331E3EFC929C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE938B47E308E6071D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7A50C1D-0083-45D6-93F7-2012DC98453A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 18-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 21-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE938B47E308E6071D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7A50C1D-0083-45D6-93F7-2012DC98453A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B81D5-EEC9-4247-BA1A-F92C17F7CDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B81D5-EEC9-4247-BA1A-F92C17F7CDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F907358-776F-4CD3-BC42-75F48DBD97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 21-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 22-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F907358-776F-4CD3-BC42-75F48DBD97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A081A7-D4CC-4A8D-84DC-0828368BCA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A081A7-D4CC-4A8D-84DC-0828368BCA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEC0E23-B86F-4D9B-BF9B-0C15892E5115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 22-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 23-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEC0E23-B86F-4D9B-BF9B-0C15892E5115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE9387996B29D7E70D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2662B577-6AB8-4260-94EF-A0A1800C5233}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D01E5AB648B5B0D02DE9387996B29D7E70D8B5D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2662B577-6AB8-4260-94EF-A0A1800C5233}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE9384C26F08AEA70D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD12BC8C-A4D4-4721-BA60-CD0921FEA005}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 23-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 24-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -46,7 +46,7 @@
     <t>Sectra (Sectra Danmark)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE9384C26F08AEA70D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD12BC8C-A4D4-4721-BA60-CD0921FEA005}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE938D46EF4AD0270D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE95B10E-4DBD-46D7-8468-36C456FFE6B5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE938D46EF4AD0270D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE95B10E-4DBD-46D7-8468-36C456FFE6B5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331FD37C-FBF2-4CB2-8151-E54F9D5C5EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 24-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 28-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331FD37C-FBF2-4CB2-8151-E54F9D5C5EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE93806B6328D8871D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7CDF41-CE0B-45A9-94A2-BB4CA21D12B9}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 28-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 02-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A081A7-D4CC-4A8D-84DC-0828368BCA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7168D9CD-FCCC-4C2E-9FB6-57DE27A755D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 22-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 07-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -46,7 +46,7 @@
     <t>Sectra (Sectra Danmark)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE93806B6328D8871D8855C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7CDF41-CE0B-45A9-94A2-BB4CA21D12B9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A81B8FE-A3F0-4F5B-99CA-838AD01E156D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 02-10-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 07-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -452,9 +452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -520,7 +520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -543,7 +543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -566,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A81B8FE-A3F0-4F5B-99CA-838AD01E156D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE938CF2E7690DA70D88558" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5313A0D8-B558-4AEC-9132-E72FADD87EFE}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 07-10-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 08-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE938CF2E7690DA70D88558" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5313A0D8-B558-4AEC-9132-E72FADD87EFE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B604425-D2AE-41B6-8D69-679C026CD85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 08-10-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 09-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B604425-D2AE-41B6-8D69-679C026CD85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666E637E-8A91-4CE5-8353-848397D4F950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/RIS-systemer_excel.XLSX
+++ b/html/RIS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666E637E-8A91-4CE5-8353-848397D4F950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BDE21BBD48B5B0D02DE9384D167188C271D88558" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF037603-10D1-4222-A792-1F037135707B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RIS_systemer">'Opdateret d. 09-10-2026'!$A$1:$G$14</definedName>
+    <definedName name="RIS_systemer">'Opdateret d. 23-10-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
